--- a/bom123.xlsx
+++ b/bom123.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODING\Line Follower Robo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODING\line follower robo car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C2B8A8-6A77-402F-B0AE-065BC21E048C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD224E78-A24C-480E-82B1-B750065C025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
